--- a/src/assets/docs/plantilla_cedula.xlsx
+++ b/src/assets/docs/plantilla_cedula.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mis Proyectos\PABS\interplazas\inter.ui\src\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A0BBCC-BA2D-4AEF-AB76-E6B2C79DDF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72CDE06-75A3-4E5D-8783-E68DBC5E6186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-708" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
   <si>
     <t>PROMOTORA FUTURA</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>{nombrePeriodo}</t>
-  </si>
-  <si>
-    <t>{FAVOR}</t>
   </si>
 </sst>
 </file>
@@ -1659,9 +1656,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" s="7" customFormat="1" ht="12.75">
-      <c r="A10" s="27" t="s">
-        <v>48</v>
-      </c>
+      <c r="A10" s="27"/>
       <c r="B10" s="27"/>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>

--- a/src/assets/docs/plantilla_cedula.xlsx
+++ b/src/assets/docs/plantilla_cedula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mis Proyectos\PABS\interplazas\inter.ui\src\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A33917-7B20-4A25-AE37-601154AAFC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EBCC63-2002-44C2-A01A-5291D134379A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,7 +449,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -561,6 +561,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="32">
@@ -600,7 +615,17 @@
   <dxfs count="52">
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
       </font>
     </dxf>
     <dxf>
@@ -610,7 +635,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color auto="1"/>
       </font>
     </dxf>
     <dxf>
@@ -620,7 +645,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
       </font>
     </dxf>
     <dxf>
@@ -630,201 +665,198 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -842,23 +874,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1313,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" style="4" customWidth="1"/>
@@ -1485,231 +1500,204 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="32" t="s">
+    <row r="13" spans="1:14" s="38" customFormat="1">
+      <c r="G13" s="39"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+    </row>
+    <row r="14" spans="1:14" s="38" customFormat="1">
+      <c r="G14" s="39"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+    </row>
+    <row r="15" spans="1:14" s="38" customFormat="1">
+      <c r="G15" s="39"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+    </row>
+    <row r="16" spans="1:14" s="38" customFormat="1">
+      <c r="G16" s="39"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+    </row>
+    <row r="17" spans="1:14" s="38" customFormat="1">
+      <c r="G17" s="39"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+    </row>
+    <row r="18" spans="1:14" s="38" customFormat="1">
+      <c r="G18" s="39"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+    </row>
+    <row r="19" spans="1:14" s="38" customFormat="1">
+      <c r="G19" s="39"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+    </row>
+    <row r="20" spans="1:14" s="38" customFormat="1">
+      <c r="G20" s="39"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+    </row>
+    <row r="21" spans="1:14" s="38" customFormat="1">
+      <c r="G21" s="39"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+    </row>
+    <row r="22" spans="1:14" s="38" customFormat="1">
+      <c r="G22" s="39"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+    </row>
+    <row r="23" spans="1:14" s="38" customFormat="1">
+      <c r="G23" s="39"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+    </row>
+    <row r="24" spans="1:14" s="38" customFormat="1">
+      <c r="G24" s="39"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+    </row>
+    <row r="25" spans="1:14" s="38" customFormat="1">
+      <c r="G25" s="39"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:14" ht="38.25">
-      <c r="A14" s="2" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="10"/>
+    </row>
+    <row r="27" spans="1:14" ht="38.25">
+      <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J27" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K27" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="5" customFormat="1" ht="12.75">
-      <c r="A15" s="19" t="s">
+    <row r="28" spans="1:14" s="5" customFormat="1" ht="12.75">
+      <c r="A28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="1:14" s="5" customFormat="1" ht="12.75">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="22"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="G17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K17" s="1">
-        <f>SUM(K15:K16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="K18" s="12"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="17" t="e">
-        <f>H11-H17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="17" t="e">
-        <f>K17-K11</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="25" t="e">
-        <f>H11*5%</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-    </row>
-    <row r="22" spans="1:11" ht="31.5">
-      <c r="A22" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="33" t="e">
-        <f>SUM(H19,K19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="10"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29" spans="1:14" s="5" customFormat="1" ht="12.75">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -1719,184 +1707,346 @@
       <c r="G29" s="19"/>
       <c r="H29" s="21"/>
       <c r="I29" s="22"/>
-      <c r="J29" s="5"/>
       <c r="K29" s="14"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="14"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="G31" s="2" t="s">
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="G30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="18">
-        <f>SUM(H29:H30)</f>
+      <c r="H30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" s="1">
+        <f>SUM(K28:K29)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="2" t="s">
+    </row>
+    <row r="31" spans="1:14" s="38" customFormat="1">
+      <c r="I31" s="12"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="17" t="e">
+        <f>H11-H30</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I32" s="8"/>
+      <c r="J32" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="17" t="e">
+        <f>K30-K11</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="25" t="e">
+        <f>H11*5%</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+    </row>
+    <row r="35" spans="1:11" ht="31.5">
+      <c r="A35" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="33" t="e">
+        <f>SUM(H32,K32)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="G44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="18">
-        <f>SUM(K29:K30)</f>
+      <c r="H44" s="18">
+        <f>SUM(H42:H43)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="31.5">
-      <c r="A32" s="28" t="s">
+      <c r="I44" s="7"/>
+      <c r="J44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="18">
+        <f>SUM(K42:K43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="31.5">
+      <c r="A45" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29">
-        <f>SUM(H29,K29)</f>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="29">
+        <f>SUM(H42,K42)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="51" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="788"/>
     <cfRule type="duplicateValues" dxfId="50" priority="789"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="790"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15:C16">
-    <cfRule type="duplicateValues" dxfId="48" priority="777"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="776"/>
+  <conditionalFormatting sqref="C28:C29">
+    <cfRule type="duplicateValues" dxfId="48" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="778"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C30">
-    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
+  <conditionalFormatting sqref="C42:C43">
+    <cfRule type="duplicateValues" dxfId="45" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
     <cfRule type="duplicateValues" dxfId="43" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="duplicateValues" dxfId="42" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="766"/>
     <cfRule type="duplicateValues" dxfId="41" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="766"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="768"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:D16">
-    <cfRule type="duplicateValues" dxfId="39" priority="780"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="779"/>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="duplicateValues" dxfId="39" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="780"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:D30">
+  <conditionalFormatting sqref="D42:D43">
     <cfRule type="duplicateValues" dxfId="37" priority="26"/>
     <cfRule type="duplicateValues" dxfId="36" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30">
+  <conditionalFormatting sqref="D43">
     <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:E16">
-    <cfRule type="duplicateValues" dxfId="34" priority="783"/>
+  <conditionalFormatting sqref="D28:E29">
+    <cfRule type="duplicateValues" dxfId="34" priority="781"/>
     <cfRule type="duplicateValues" dxfId="33" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="783"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:E30">
+  <conditionalFormatting sqref="D42:E43">
     <cfRule type="duplicateValues" dxfId="31" priority="27"/>
     <cfRule type="duplicateValues" dxfId="30" priority="28"/>
     <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30:E30">
+  <conditionalFormatting sqref="D43:E43">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
     <cfRule type="duplicateValues" dxfId="27" priority="31"/>
     <cfRule type="duplicateValues" dxfId="26" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="25" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="791"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="797"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E16">
+  <conditionalFormatting sqref="E28:E29">
     <cfRule type="duplicateValues" dxfId="18" priority="784"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="786"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="787"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="787"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E29:E30">
-    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="38"/>
+  <conditionalFormatting sqref="E42:E43">
+    <cfRule type="duplicateValues" dxfId="14" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19:H20">
+  <conditionalFormatting sqref="H32:H33">
     <cfRule type="cellIs" dxfId="10" priority="522" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="525" operator="lessThan">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" priority="528" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="525" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19:K19 H20">
+  <conditionalFormatting sqref="H32:K32 H33">
     <cfRule type="cellIs" dxfId="8" priority="530" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:K22">
+  <conditionalFormatting sqref="H35:K35">
     <cfRule type="cellIs" dxfId="7" priority="520" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="529" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="523" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="523" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="529" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32:K32">
+  <conditionalFormatting sqref="H45:K45">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="25" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="24" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="25" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19">
-    <cfRule type="cellIs" dxfId="1" priority="524" operator="lessThan">
+  <conditionalFormatting sqref="K32">
+    <cfRule type="cellIs" dxfId="1" priority="521" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="521" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="524" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/src/assets/docs/plantilla_cedula.xlsx
+++ b/src/assets/docs/plantilla_cedula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mis Proyectos\PABS\interplazas\inter.ui\src\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6618F8C3-1D0E-4CCB-83AA-11E0F684C347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A179B0-C425-40E1-9B32-763679DA0FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,69 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>PROMOTORA FUTURA</t>
-  </si>
-  <si>
-    <t>TITULAR</t>
-  </si>
-  <si>
-    <t>FINADO</t>
-  </si>
-  <si>
-    <t>CONTRATO</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>CONCEPTO</t>
-  </si>
-  <si>
-    <t>MONTO</t>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t>SALDO PABS*</t>
-  </si>
-  <si>
-    <t>SALDOS EFECTIVAMENTE COBRADOS</t>
-  </si>
-  <si>
-    <t>OBSERVACION</t>
-  </si>
-  <si>
-    <t>FILIAL ORIGEN</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SERVICIOS OTORGADOS EN SUCURSAL | POR </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>COBRAR</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A FAVOR DE LA FILIAL</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">ESTADO DE CUENTA: SERVICIOS CCI </t>
@@ -107,30 +47,20 @@
     <t>*El saldo PABS es un dato solamente informativo que no afecta el total a pagar. Es responsabilidad de cada sucursal cobrar al cliente y depositar a la filial origen del contrato. Favor de revisar estos saldos y confirmar los montos para realizar las aclaraciones</t>
   </si>
   <si>
-    <t>FILIAL OTORGANTE</t>
-  </si>
-  <si>
     <t>FILIAL {nombreFilial}</t>
   </si>
   <si>
     <t>PERIODO: {nombrePeriodo}</t>
-  </si>
-  <si>
-    <t>{subtotalFAVOR}</t>
-  </si>
-  <si>
-    <t>{saldosCobrados}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-1540A]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,14 +71,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -177,14 +99,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -201,17 +115,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri "/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -223,7 +127,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,12 +146,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -263,7 +161,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -292,81 +190,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -404,99 +260,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -863,255 +627,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" style="4" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="4"/>
-    <col min="8" max="8" width="16.5703125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.42578125" style="14" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="6" customWidth="1"/>
-    <col min="12" max="14" width="11.42578125" style="8"/>
-    <col min="15" max="16384" width="11.42578125" style="4"/>
+    <col min="1" max="1" width="17.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="11.42578125" style="1"/>
+    <col min="8" max="8" width="16.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.42578125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" style="2" customWidth="1"/>
+    <col min="12" max="14" width="11.42578125" style="3"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-    </row>
-    <row r="3" spans="1:14" ht="18.75">
-      <c r="A3" s="24" t="s">
-        <v>16</v>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>3</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="M5" s="10"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:14" ht="38.25">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="12.75">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G9" s="6"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G11" s="6"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="19"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="19"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="G15" s="19"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="19"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="7:11">
-      <c r="G17" s="19"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="7:11">
-      <c r="G18" s="19"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="10"/>
-    </row>
-    <row r="19" spans="7:11">
-      <c r="G19" s="19"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="10"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G12" s="6"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G13" s="6"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
   </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="12" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="789"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="790"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="duplicateValues" dxfId="9" priority="766"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="768"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="6" priority="791"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="796"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="797"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
